--- a/SAP Reports/Input Files/Bal-Sht Jan 26/BS CHALLPG JAN 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/Bal-Sht Jan 26/BS CHALLPG JAN 26 ANNUAL.xlsx
@@ -14,78 +14,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="72">
   <si>
     <t>Account Name</t>
   </si>
   <si>
-    <t>Current Period</t>
-  </si>
-  <si>
-    <t>Comparison Period</t>
-  </si>
-  <si>
-    <t>Difference Amount</t>
-  </si>
-  <si>
-    <t>Percentage Difference</t>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>System Currency</t>
   </si>
   <si>
     <t>Assets</t>
   </si>
   <si>
-    <t>$  604,648.08</t>
-  </si>
-  <si>
-    <t>$  798,778.94</t>
-  </si>
-  <si>
-    <t>$ -194,130.86</t>
-  </si>
-  <si>
-    <t>% -24.303</t>
+    <t>$  553,397.11</t>
   </si>
   <si>
     <t>Current Assets - Cash and Equiv</t>
   </si>
   <si>
-    <t>$  582,648.08</t>
-  </si>
-  <si>
-    <t>$ -216,130.86</t>
-  </si>
-  <si>
-    <t>% -27.058</t>
+    <t>$  531,397.11</t>
   </si>
   <si>
     <t>Cash and Equiv - CASH AND EQUITY</t>
   </si>
   <si>
-    <t>$ (1,957,617.97)</t>
-  </si>
-  <si>
-    <t>$ (227,868.11)</t>
-  </si>
-  <si>
-    <t>$ -1,729,749.86</t>
-  </si>
-  <si>
-    <t>% -759.101</t>
+    <t>$ (1,957,820.30)</t>
   </si>
   <si>
     <t>110101-02-000-00 - SSB-CHECKING ACCT</t>
   </si>
   <si>
-    <t>$  42,382.03</t>
-  </si>
-  <si>
-    <t>$  472,131.89</t>
-  </si>
-  <si>
-    <t>$ -429,749.86</t>
-  </si>
-  <si>
-    <t>% -91.023</t>
+    <t>$  42,179.70</t>
   </si>
   <si>
     <t>110150-02-000-00 - INTER DIVISION BANK</t>
@@ -94,15 +55,6 @@
     <t>$ (2,000,000.00)</t>
   </si>
   <si>
-    <t>$ (700,000.00)</t>
-  </si>
-  <si>
-    <t>$ -1,300,000.00</t>
-  </si>
-  <si>
-    <t>% -185.714</t>
-  </si>
-  <si>
     <t>__________________</t>
   </si>
   <si>
@@ -115,16 +67,7 @@
     <t>Receivables - RECEIVABLES</t>
   </si>
   <si>
-    <t>$  2,540,266.05</t>
-  </si>
-  <si>
-    <t>$  1,026,647.05</t>
-  </si>
-  <si>
-    <t>$ 1,513,619.00</t>
-  </si>
-  <si>
-    <t>% 147.433</t>
+    <t>$  2,489,217.41</t>
   </si>
   <si>
     <t>120000-02-000-00 - ACCOUNTS RECEIVABLE</t>
@@ -148,12 +91,6 @@
     <t>$  22,000.00</t>
   </si>
   <si>
-    <t>$ 22,000.00</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
     <t>FixedAssets - FIXED ASSETS</t>
   </si>
   <si>
@@ -181,16 +118,7 @@
     <t>Liabilities</t>
   </si>
   <si>
-    <t>$  197,541.57</t>
-  </si>
-  <si>
-    <t>$  631,978.68</t>
-  </si>
-  <si>
-    <t>$ -434,437.11</t>
-  </si>
-  <si>
-    <t>% -68.742</t>
+    <t>$  197,339.24</t>
   </si>
   <si>
     <t>Current Liabs - CURRENT LIABILITIES</t>
@@ -199,15 +127,6 @@
     <t>Accts Payable - ACCOUNTS PAYABLE</t>
   </si>
   <si>
-    <t>$  202.33</t>
-  </si>
-  <si>
-    <t>$ 202.33</t>
-  </si>
-  <si>
-    <t>220040-02-000-00 - ACCOUNTS PAYABLE</t>
-  </si>
-  <si>
     <t>Total Accts Payable - ACCOUNTS PAYABLE</t>
   </si>
   <si>
@@ -217,39 +136,18 @@
     <t>$  197,217.94</t>
   </si>
   <si>
-    <t>$ -434,760.74</t>
-  </si>
-  <si>
-    <t>% -68.794</t>
-  </si>
-  <si>
-    <t>220256-02-000-00 - WAGES PAYABLES</t>
+    <t>220256-02-000-00 - SALARY ACCRUAL</t>
   </si>
   <si>
     <t>$  206,216.36</t>
   </si>
   <si>
-    <t>$  629,390.65</t>
-  </si>
-  <si>
-    <t>$ -423,174.29</t>
-  </si>
-  <si>
-    <t>% -67.236</t>
-  </si>
-  <si>
     <t>250900-02-000-00 - 401 K LIABILITY -PAYABLE</t>
   </si>
   <si>
     <t>$ (10,978.42)</t>
   </si>
   <si>
-    <t>$  608.03</t>
-  </si>
-  <si>
-    <t>$ -11,586.45</t>
-  </si>
-  <si>
     <t>250950-02-000-00 - UNION DUES PAYABLE</t>
   </si>
   <si>
@@ -265,10 +163,7 @@
     <t>$  121.30</t>
   </si>
   <si>
-    <t>$ 121.30</t>
-  </si>
-  <si>
-    <t>250920-02-000-00 - HUMA DENTAL &amp; VISION INS</t>
+    <t>250920-02-000-00 - HUMANA DEN &amp; VIS INS</t>
   </si>
   <si>
     <t>Total OtherLiability - OTHER LIBILITY</t>
@@ -295,21 +190,15 @@
     <t>Equity</t>
   </si>
   <si>
-    <t>$  407,106.51</t>
-  </si>
-  <si>
-    <t>$  166,800.26</t>
-  </si>
-  <si>
-    <t>$ 240,306.25</t>
-  </si>
-  <si>
-    <t>% 144.068</t>
+    <t>$  356,057.87</t>
   </si>
   <si>
     <t>Stock Equity - STOCK HOLDERS EQUITY</t>
   </si>
   <si>
+    <t>$  155,537.56</t>
+  </si>
+  <si>
     <t>Common Stock - COMMON STOCK</t>
   </si>
   <si>
@@ -325,6 +214,9 @@
     <t>Surplus - SURPLUS</t>
   </si>
   <si>
+    <t>368400-02-000-00 - RETAINED EARNINGS</t>
+  </si>
+  <si>
     <t>Total Surplus - SURPLUS</t>
   </si>
   <si>
@@ -332,6 +224,9 @@
   </si>
   <si>
     <t>Profit Period</t>
+  </si>
+  <si>
+    <t>$  200,520.31</t>
   </si>
   <si>
     <t>Total Equity</t>
@@ -1192,1054 +1087,883 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
 		</row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
 		</row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
 		</row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
 		</row>
     <row r="14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
 		</row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
 		</row>
     <row r="21">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
 		</row>
     <row r="23">
       <c r="B23" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
 		</row>
     <row r="27">
       <c r="B27" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
 		</row>
     <row r="31">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="32">
 		</row>
     <row r="33">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="34">
 		</row>
     <row r="35">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
 		</row>
     <row r="40">
       <c r="A40" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
 		</row>
     <row r="42">
       <c r="B42" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
 		</row>
     <row r="46">
       <c r="B46" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
 		</row>
     <row r="50">
       <c r="B50" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
 		</row>
     <row r="56">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
-      </c>
-      <c r="D56" t="s">
-        <v>57</v>
-      </c>
-      <c r="E56" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
 		</row>
     <row r="58">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
 		</row>
     <row r="60">
       <c r="A60" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" t="s">
-        <v>61</v>
-      </c>
-      <c r="D60" t="s">
-        <v>62</v>
-      </c>
-      <c r="E60" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
 		</row>
     <row r="62">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
       <c r="B62" t="s">
-        <v>61</v>
-      </c>
-      <c r="D62" t="s">
-        <v>62</v>
-      </c>
-      <c r="E62" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="s">
-        <v>29</v>
-      </c>
-      <c r="C63" t="s">
-        <v>29</v>
+      <c r="A63" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
-        <v>64</v>
-      </c>
       <c r="B64" t="s">
-        <v>61</v>
-      </c>
-      <c r="D64" t="s">
-        <v>62</v>
-      </c>
-      <c r="E64" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="66">
-		</row>
+      <c r="A66" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" t="s">
-        <v>66</v>
-      </c>
-      <c r="C67" t="s">
-        <v>56</v>
-      </c>
-      <c r="D67" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" t="s">
-        <v>68</v>
-      </c>
-    </row>
+		</row>
     <row r="68">
-		</row>
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
-      </c>
-      <c r="D69" t="s">
-        <v>72</v>
-      </c>
-      <c r="E69" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
-        <v>78</v>
-      </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="s">
+        <v>46</v>
+      </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
-        <v>80</v>
-      </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>56</v>
-      </c>
-      <c r="D73" t="s">
-        <v>67</v>
-      </c>
-      <c r="E73" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="75">
-		</row>
+      <c r="A75" t="s">
+        <v>47</v>
+      </c>
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" t="s">
-        <v>83</v>
-      </c>
-      <c r="E76" t="s">
-        <v>45</v>
-      </c>
-    </row>
+		</row>
     <row r="77">
-		</row>
+      <c r="A77" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="78">
-      <c r="A78" t="s">
-        <v>84</v>
-      </c>
       <c r="B78" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" t="s">
-        <v>83</v>
-      </c>
-      <c r="E78" t="s">
-        <v>45</v>
+        <v>13</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="s">
+        <v>50</v>
+      </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="s">
-        <v>85</v>
-      </c>
       <c r="B80" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" t="s">
-        <v>83</v>
-      </c>
-      <c r="E80" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="82">
-		</row>
+      <c r="B82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="83">
+      <c r="A83" t="s">
+        <v>51</v>
+      </c>
       <c r="B83" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s">
-        <v>86</v>
-      </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>56</v>
-      </c>
-      <c r="D84" t="s">
-        <v>57</v>
-      </c>
-      <c r="E84" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="86">
-		</row>
+      <c r="A86" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" t="s">
-        <v>87</v>
-      </c>
-    </row>
+		</row>
     <row r="88">
-		</row>
+      <c r="A88" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="89">
-      <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
+		</row>
     <row r="90">
-		</row>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="91">
-      <c r="B91" t="s">
-        <v>29</v>
-      </c>
-      <c r="C91" t="s">
-        <v>29</v>
+      <c r="A91" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="s">
-        <v>89</v>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="s">
-        <v>29</v>
-      </c>
-      <c r="C94" t="s">
-        <v>29</v>
+      <c r="A94" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="s">
-        <v>90</v>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="s">
+        <v>56</v>
+      </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
-      </c>
-      <c r="D98" t="s">
-        <v>57</v>
-      </c>
-      <c r="E98" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" t="s">
-        <v>93</v>
-      </c>
-      <c r="C99" t="s">
-        <v>94</v>
-      </c>
-      <c r="D99" t="s">
-        <v>95</v>
-      </c>
-      <c r="E99" t="s">
-        <v>96</v>
-      </c>
-    </row>
+		</row>
     <row r="100">
-		</row>
+      <c r="A100" t="s">
+        <v>59</v>
+      </c>
+      <c r="B100" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="101">
-      <c r="A101" t="s">
-        <v>97</v>
-      </c>
-    </row>
+		</row>
     <row r="102">
-		</row>
+      <c r="A102" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="103">
-      <c r="A103" t="s">
-        <v>98</v>
-      </c>
-    </row>
+		</row>
     <row r="104">
-		</row>
+      <c r="B104" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="105">
-      <c r="B105" t="s">
-        <v>29</v>
-      </c>
-      <c r="C105" t="s">
-        <v>29</v>
+      <c r="A105" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="s">
-        <v>99</v>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="s">
-        <v>31</v>
-      </c>
-      <c r="C107" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="108">
-		</row>
+      <c r="A108" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="109">
-      <c r="A109" t="s">
-        <v>100</v>
-      </c>
-    </row>
+		</row>
     <row r="110">
-		</row>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="111">
-      <c r="B111" t="s">
-        <v>29</v>
-      </c>
-      <c r="C111" t="s">
-        <v>29</v>
+      <c r="A111" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s">
-        <v>101</v>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="s">
-        <v>31</v>
-      </c>
-      <c r="C113" t="s">
-        <v>31</v>
-      </c>
-    </row>
+		</row>
     <row r="114">
-		</row>
+      <c r="A114" t="s">
+        <v>65</v>
+      </c>
+      <c r="B114" t="s">
+        <v>60</v>
+      </c>
+      <c r="C114" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="115">
-      <c r="A115" t="s">
-        <v>102</v>
-      </c>
-    </row>
+		</row>
     <row r="116">
-		</row>
+      <c r="A116" t="s">
+        <v>66</v>
+      </c>
+      <c r="B116" t="s">
+        <v>60</v>
+      </c>
+      <c r="C116" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="117">
       <c r="B117" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>103</v>
+        <v>67</v>
+      </c>
+      <c r="B118" t="s">
+        <v>60</v>
+      </c>
+      <c r="C118" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>104</v>
+        <v>68</v>
+      </c>
+      <c r="B121" t="s">
+        <v>60</v>
+      </c>
+      <c r="C121" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B123" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C123" t="s">
-        <v>94</v>
-      </c>
-      <c r="D123" t="s">
-        <v>95</v>
-      </c>
-      <c r="E123" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="C125" t="s">
-        <v>94</v>
-      </c>
-      <c r="D125" t="s">
-        <v>95</v>
-      </c>
-      <c r="E125" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>7</v>
-      </c>
-      <c r="D127" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C128" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129">
